--- a/data/gathering.xlsx
+++ b/data/gathering.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Training\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BED154F-266E-43F8-A6A4-EADE15F93496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24F39C8-A44B-4AE5-A4B8-7C99FF95E6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26325" yWindow="2265" windowWidth="23235" windowHeight="12090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24660" yWindow="6405" windowWidth="18585" windowHeight="9675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gathering" sheetId="1" r:id="rId1"/>
@@ -63,9 +63,6 @@
     <t>標題</t>
   </si>
   <si>
-    <t>項目內容</t>
-  </si>
-  <si>
     <t>創建日期</t>
   </si>
   <si>
@@ -263,6 +260,10 @@
   </si>
   <si>
     <t>OTHER</t>
+  </si>
+  <si>
+    <t>項目內容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -272,7 +273,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -676,15 +677,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P160"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="13" width="28.625" style="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>9</v>
@@ -693,31 +694,31 @@
         <v>10</v>
       </c>
       <c r="D1" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>13</v>
       </c>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
@@ -734,7 +735,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>5</v>
@@ -752,7 +753,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:16" s="11" customFormat="1">
+    <row r="3" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -760,28 +761,28 @@
         <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -789,7 +790,7 @@
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:16" s="11" customFormat="1">
+    <row r="4" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -797,28 +798,28 @@
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -827,7 +828,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
     </row>
-    <row r="5" spans="1:16" s="11" customFormat="1">
+    <row r="5" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -835,28 +836,28 @@
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -865,7 +866,7 @@
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -873,28 +874,28 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -903,7 +904,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -911,34 +912,34 @@
         <v>5</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -946,28 +947,28 @@
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -976,7 +977,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -984,28 +985,28 @@
         <v>2</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -1014,7 +1015,7 @@
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1022,28 +1023,28 @@
         <v>2</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>35</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -1052,7 +1053,7 @@
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1060,28 +1061,28 @@
         <v>2</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -1090,7 +1091,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1098,28 +1099,28 @@
         <v>10</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -1128,7 +1129,7 @@
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1136,28 +1137,28 @@
         <v>10</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -1166,7 +1167,7 @@
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1174,28 +1175,28 @@
         <v>12</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E14" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -1204,7 +1205,7 @@
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1222,7 +1223,7 @@
       <c r="O15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1239,7 +1240,7 @@
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -1256,7 +1257,7 @@
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1273,7 +1274,7 @@
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1290,7 +1291,7 @@
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1304,7 +1305,7 @@
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1318,7 +1319,7 @@
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1332,7 +1333,7 @@
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1346,7 +1347,7 @@
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1360,7 +1361,7 @@
       <c r="O24" s="6"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1374,7 +1375,7 @@
       <c r="O25" s="6"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1388,7 +1389,7 @@
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1402,7 +1403,7 @@
       <c r="O27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1416,7 +1417,7 @@
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1430,7 +1431,7 @@
       <c r="O29" s="6"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1444,7 +1445,7 @@
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1459,7 +1460,7 @@
       <c r="O31" s="6"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1474,7 +1475,7 @@
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -1492,7 +1493,7 @@
       <c r="O33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1510,7 +1511,7 @@
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1528,7 +1529,7 @@
       <c r="O35" s="6"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -1546,7 +1547,7 @@
       <c r="O36" s="6"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1564,7 +1565,7 @@
       <c r="O37" s="6"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1582,7 +1583,7 @@
       <c r="O38" s="6"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1600,7 +1601,7 @@
       <c r="O39" s="6"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1618,7 +1619,7 @@
       <c r="O40" s="6"/>
       <c r="P40" s="6"/>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1636,7 +1637,7 @@
       <c r="O41" s="6"/>
       <c r="P41" s="6"/>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -1654,7 +1655,7 @@
       <c r="O42" s="6"/>
       <c r="P42" s="6"/>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1672,7 +1673,7 @@
       <c r="O43" s="6"/>
       <c r="P43" s="6"/>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -1690,7 +1691,7 @@
       <c r="O44" s="6"/>
       <c r="P44" s="6"/>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -1708,7 +1709,7 @@
       <c r="O45" s="6"/>
       <c r="P45" s="6"/>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -1726,7 +1727,7 @@
       <c r="O46" s="6"/>
       <c r="P46" s="6"/>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -1744,7 +1745,7 @@
       <c r="O47" s="6"/>
       <c r="P47" s="6"/>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -1762,7 +1763,7 @@
       <c r="O48" s="6"/>
       <c r="P48" s="6"/>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -1780,7 +1781,7 @@
       <c r="O49" s="6"/>
       <c r="P49" s="6"/>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -1798,7 +1799,7 @@
       <c r="O50" s="6"/>
       <c r="P50" s="6"/>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -1816,7 +1817,7 @@
       <c r="O51" s="6"/>
       <c r="P51" s="6"/>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -1834,7 +1835,7 @@
       <c r="O52" s="6"/>
       <c r="P52" s="6"/>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -1852,7 +1853,7 @@
       <c r="O53" s="6"/>
       <c r="P53" s="6"/>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -1870,7 +1871,7 @@
       <c r="O54" s="6"/>
       <c r="P54" s="6"/>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="2"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -1888,7 +1889,7 @@
       <c r="O55" s="6"/>
       <c r="P55" s="6"/>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="2"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -1906,7 +1907,7 @@
       <c r="O56" s="6"/>
       <c r="P56" s="6"/>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="2"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -1924,7 +1925,7 @@
       <c r="O57" s="6"/>
       <c r="P57" s="6"/>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="2"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -1942,7 +1943,7 @@
       <c r="O58" s="6"/>
       <c r="P58" s="6"/>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="2"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -1960,7 +1961,7 @@
       <c r="O59" s="6"/>
       <c r="P59" s="6"/>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="2"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -1978,7 +1979,7 @@
       <c r="O60" s="6"/>
       <c r="P60" s="6"/>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="2"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -1996,7 +1997,7 @@
       <c r="O61" s="6"/>
       <c r="P61" s="6"/>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="2"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -2014,7 +2015,7 @@
       <c r="O62" s="6"/>
       <c r="P62" s="6"/>
     </row>
-    <row r="63" spans="1:16">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="2"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -2032,7 +2033,7 @@
       <c r="O63" s="6"/>
       <c r="P63" s="6"/>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="2"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -2050,7 +2051,7 @@
       <c r="O64" s="6"/>
       <c r="P64" s="6"/>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="2"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -2068,7 +2069,7 @@
       <c r="O65" s="6"/>
       <c r="P65" s="6"/>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="2"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -2086,7 +2087,7 @@
       <c r="O66" s="6"/>
       <c r="P66" s="6"/>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="2"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -2104,7 +2105,7 @@
       <c r="O67" s="6"/>
       <c r="P67" s="6"/>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="2"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -2122,7 +2123,7 @@
       <c r="O68" s="6"/>
       <c r="P68" s="6"/>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="2"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -2140,7 +2141,7 @@
       <c r="O69" s="6"/>
       <c r="P69" s="6"/>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="2"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -2158,7 +2159,7 @@
       <c r="O70" s="6"/>
       <c r="P70" s="6"/>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="2"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -2176,7 +2177,7 @@
       <c r="O71" s="6"/>
       <c r="P71" s="6"/>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="2"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -2194,7 +2195,7 @@
       <c r="O72" s="6"/>
       <c r="P72" s="6"/>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" s="2"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -2212,7 +2213,7 @@
       <c r="O73" s="6"/>
       <c r="P73" s="6"/>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" s="2"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2230,7 +2231,7 @@
       <c r="O74" s="6"/>
       <c r="P74" s="6"/>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="2"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -2248,7 +2249,7 @@
       <c r="O75" s="6"/>
       <c r="P75" s="6"/>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="2"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -2266,7 +2267,7 @@
       <c r="O76" s="6"/>
       <c r="P76" s="6"/>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" s="2"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -2284,7 +2285,7 @@
       <c r="O77" s="6"/>
       <c r="P77" s="6"/>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="2"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -2302,7 +2303,7 @@
       <c r="O78" s="6"/>
       <c r="P78" s="6"/>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" s="2"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -2320,7 +2321,7 @@
       <c r="O79" s="6"/>
       <c r="P79" s="6"/>
     </row>
-    <row r="80" spans="1:16">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" s="2"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -2338,7 +2339,7 @@
       <c r="O80" s="6"/>
       <c r="P80" s="6"/>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="2"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -2356,7 +2357,7 @@
       <c r="O81" s="6"/>
       <c r="P81" s="6"/>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -2374,7 +2375,7 @@
       <c r="O82" s="6"/>
       <c r="P82" s="6"/>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="2"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -2392,7 +2393,7 @@
       <c r="O83" s="6"/>
       <c r="P83" s="6"/>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="2"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -2410,7 +2411,7 @@
       <c r="O84" s="6"/>
       <c r="P84" s="6"/>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="2"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -2428,7 +2429,7 @@
       <c r="O85" s="6"/>
       <c r="P85" s="6"/>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="2"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -2446,7 +2447,7 @@
       <c r="O86" s="6"/>
       <c r="P86" s="6"/>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="2"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -2464,7 +2465,7 @@
       <c r="O87" s="6"/>
       <c r="P87" s="6"/>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="2"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -2482,7 +2483,7 @@
       <c r="O88" s="6"/>
       <c r="P88" s="6"/>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="2"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -2500,7 +2501,7 @@
       <c r="O89" s="6"/>
       <c r="P89" s="6"/>
     </row>
-    <row r="90" spans="1:16">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="2"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -2518,7 +2519,7 @@
       <c r="O90" s="6"/>
       <c r="P90" s="6"/>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="2"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -2536,7 +2537,7 @@
       <c r="O91" s="6"/>
       <c r="P91" s="6"/>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="2"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -2554,7 +2555,7 @@
       <c r="O92" s="6"/>
       <c r="P92" s="6"/>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="2"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -2572,7 +2573,7 @@
       <c r="O93" s="6"/>
       <c r="P93" s="6"/>
     </row>
-    <row r="94" spans="1:16">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" s="2"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -2590,7 +2591,7 @@
       <c r="O94" s="6"/>
       <c r="P94" s="6"/>
     </row>
-    <row r="95" spans="1:16">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="2"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -2608,7 +2609,7 @@
       <c r="O95" s="6"/>
       <c r="P95" s="6"/>
     </row>
-    <row r="96" spans="1:16">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" s="2"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -2626,7 +2627,7 @@
       <c r="O96" s="6"/>
       <c r="P96" s="6"/>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="2"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -2644,7 +2645,7 @@
       <c r="O97" s="6"/>
       <c r="P97" s="6"/>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="2"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -2662,7 +2663,7 @@
       <c r="O98" s="6"/>
       <c r="P98" s="6"/>
     </row>
-    <row r="99" spans="1:16">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="2"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -2677,7 +2678,7 @@
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="2"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -2692,7 +2693,7 @@
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="2"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -2707,7 +2708,7 @@
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
     </row>
-    <row r="102" spans="1:16">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" s="2"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -2722,7 +2723,7 @@
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
     </row>
-    <row r="103" spans="1:16">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" s="2"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -2737,7 +2738,7 @@
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
     </row>
-    <row r="104" spans="1:16">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="2"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -2752,7 +2753,7 @@
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
     </row>
-    <row r="105" spans="1:16">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" s="2"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -2767,7 +2768,7 @@
       <c r="L105" s="3"/>
       <c r="M105" s="3"/>
     </row>
-    <row r="106" spans="1:16">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" s="2"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -2782,7 +2783,7 @@
       <c r="L106" s="3"/>
       <c r="M106" s="3"/>
     </row>
-    <row r="107" spans="1:16">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" s="2"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -2797,7 +2798,7 @@
       <c r="L107" s="3"/>
       <c r="M107" s="3"/>
     </row>
-    <row r="108" spans="1:16">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="2"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -2812,7 +2813,7 @@
       <c r="L108" s="3"/>
       <c r="M108" s="3"/>
     </row>
-    <row r="109" spans="1:16">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -2827,7 +2828,7 @@
       <c r="L109" s="3"/>
       <c r="M109" s="3"/>
     </row>
-    <row r="110" spans="1:16">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -2842,7 +2843,7 @@
       <c r="L110" s="3"/>
       <c r="M110" s="3"/>
     </row>
-    <row r="111" spans="1:16">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" s="2"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -2857,7 +2858,7 @@
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
     </row>
-    <row r="112" spans="1:16">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="2"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -2872,7 +2873,7 @@
       <c r="L112" s="3"/>
       <c r="M112" s="3"/>
     </row>
-    <row r="113" spans="1:13">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="2"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -2887,7 +2888,7 @@
       <c r="L113" s="3"/>
       <c r="M113" s="3"/>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="2"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -2902,7 +2903,7 @@
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="2"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -2917,7 +2918,7 @@
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
     </row>
-    <row r="116" spans="1:13">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="2"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -2932,7 +2933,7 @@
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
     </row>
-    <row r="117" spans="1:13">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="2"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -2947,7 +2948,7 @@
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="2"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -2962,7 +2963,7 @@
       <c r="L118" s="3"/>
       <c r="M118" s="3"/>
     </row>
-    <row r="119" spans="1:13">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="2"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -2977,7 +2978,7 @@
       <c r="L119" s="3"/>
       <c r="M119" s="3"/>
     </row>
-    <row r="120" spans="1:13">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="2"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -2992,7 +2993,7 @@
       <c r="L120" s="3"/>
       <c r="M120" s="3"/>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="2"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -3007,7 +3008,7 @@
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="2"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -3022,7 +3023,7 @@
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="2"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -3037,7 +3038,7 @@
       <c r="L123" s="3"/>
       <c r="M123" s="3"/>
     </row>
-    <row r="124" spans="1:13">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="2"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -3052,7 +3053,7 @@
       <c r="L124" s="3"/>
       <c r="M124" s="3"/>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="2"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -3067,7 +3068,7 @@
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="2"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -3082,7 +3083,7 @@
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="2"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -3097,7 +3098,7 @@
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="2"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -3112,7 +3113,7 @@
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="2"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -3127,7 +3128,7 @@
       <c r="L129" s="3"/>
       <c r="M129" s="3"/>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="2"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -3142,7 +3143,7 @@
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="2"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -3157,7 +3158,7 @@
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="2"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -3172,7 +3173,7 @@
       <c r="L132" s="3"/>
       <c r="M132" s="3"/>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="2"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -3187,7 +3188,7 @@
       <c r="L133" s="3"/>
       <c r="M133" s="3"/>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="2"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -3202,7 +3203,7 @@
       <c r="L134" s="3"/>
       <c r="M134" s="3"/>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="2"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -3217,7 +3218,7 @@
       <c r="L135" s="3"/>
       <c r="M135" s="3"/>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F136" s="8"/>
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
@@ -3226,7 +3227,7 @@
       <c r="K136" s="8"/>
       <c r="L136" s="8"/>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F137" s="8"/>
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
@@ -3235,7 +3236,7 @@
       <c r="K137" s="8"/>
       <c r="L137" s="8"/>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F138" s="8"/>
       <c r="G138" s="8"/>
       <c r="H138" s="8"/>
@@ -3244,7 +3245,7 @@
       <c r="K138" s="8"/>
       <c r="L138" s="8"/>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F139" s="8"/>
       <c r="G139" s="8"/>
       <c r="H139" s="8"/>
@@ -3253,7 +3254,7 @@
       <c r="K139" s="8"/>
       <c r="L139" s="8"/>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F140" s="8"/>
       <c r="G140" s="8"/>
       <c r="H140" s="8"/>
@@ -3262,7 +3263,7 @@
       <c r="K140" s="8"/>
       <c r="L140" s="8"/>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F141" s="8"/>
       <c r="G141" s="8"/>
       <c r="H141" s="8"/>
@@ -3271,7 +3272,7 @@
       <c r="K141" s="8"/>
       <c r="L141" s="8"/>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F142" s="8"/>
       <c r="G142" s="8"/>
       <c r="H142" s="8"/>
@@ -3280,7 +3281,7 @@
       <c r="K142" s="8"/>
       <c r="L142" s="8"/>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F143" s="8"/>
       <c r="G143" s="8"/>
       <c r="H143" s="8"/>
@@ -3289,7 +3290,7 @@
       <c r="K143" s="8"/>
       <c r="L143" s="8"/>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F144" s="8"/>
       <c r="G144" s="8"/>
       <c r="H144" s="8"/>
@@ -3298,7 +3299,7 @@
       <c r="K144" s="8"/>
       <c r="L144" s="8"/>
     </row>
-    <row r="145" spans="6:12">
+    <row r="145" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F145" s="8"/>
       <c r="G145" s="8"/>
       <c r="H145" s="8"/>
@@ -3307,77 +3308,77 @@
       <c r="K145" s="8"/>
       <c r="L145" s="8"/>
     </row>
-    <row r="146" spans="6:12">
+    <row r="146" spans="6:12" x14ac:dyDescent="0.3">
       <c r="J146" s="5"/>
       <c r="K146" s="5"/>
       <c r="L146" s="5"/>
     </row>
-    <row r="147" spans="6:12">
+    <row r="147" spans="6:12" x14ac:dyDescent="0.3">
       <c r="J147" s="5"/>
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
     </row>
-    <row r="148" spans="6:12">
+    <row r="148" spans="6:12" x14ac:dyDescent="0.3">
       <c r="J148" s="5"/>
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
     </row>
-    <row r="149" spans="6:12">
+    <row r="149" spans="6:12" x14ac:dyDescent="0.3">
       <c r="J149" s="5"/>
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
     </row>
-    <row r="150" spans="6:12">
+    <row r="150" spans="6:12" x14ac:dyDescent="0.3">
       <c r="J150" s="5"/>
       <c r="K150" s="5"/>
       <c r="L150" s="5"/>
     </row>
-    <row r="151" spans="6:12">
+    <row r="151" spans="6:12" x14ac:dyDescent="0.3">
       <c r="J151" s="5"/>
       <c r="K151" s="5"/>
       <c r="L151" s="5"/>
     </row>
-    <row r="152" spans="6:12">
+    <row r="152" spans="6:12" x14ac:dyDescent="0.3">
       <c r="J152" s="5"/>
       <c r="K152" s="5"/>
       <c r="L152" s="5"/>
     </row>
-    <row r="153" spans="6:12">
+    <row r="153" spans="6:12" x14ac:dyDescent="0.3">
       <c r="J153" s="5"/>
       <c r="K153" s="5"/>
       <c r="L153" s="5"/>
     </row>
-    <row r="154" spans="6:12">
+    <row r="154" spans="6:12" x14ac:dyDescent="0.3">
       <c r="J154" s="5"/>
       <c r="K154" s="5"/>
       <c r="L154" s="5"/>
     </row>
-    <row r="155" spans="6:12">
+    <row r="155" spans="6:12" x14ac:dyDescent="0.3">
       <c r="J155" s="5"/>
       <c r="K155" s="5"/>
       <c r="L155" s="5"/>
     </row>
-    <row r="156" spans="6:12">
+    <row r="156" spans="6:12" x14ac:dyDescent="0.3">
       <c r="J156" s="5"/>
       <c r="K156" s="5"/>
       <c r="L156" s="5"/>
     </row>
-    <row r="157" spans="6:12">
+    <row r="157" spans="6:12" x14ac:dyDescent="0.3">
       <c r="J157" s="5"/>
       <c r="K157" s="5"/>
       <c r="L157" s="5"/>
     </row>
-    <row r="158" spans="6:12">
+    <row r="158" spans="6:12" x14ac:dyDescent="0.3">
       <c r="J158" s="5"/>
       <c r="K158" s="5"/>
       <c r="L158" s="5"/>
     </row>
-    <row r="159" spans="6:12">
+    <row r="159" spans="6:12" x14ac:dyDescent="0.3">
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
       <c r="L159" s="5"/>
     </row>
-    <row r="160" spans="6:12">
+    <row r="160" spans="6:12" x14ac:dyDescent="0.3">
       <c r="J160" s="5"/>
       <c r="K160" s="5"/>
       <c r="L160" s="5"/>

--- a/data/gathering.xlsx
+++ b/data/gathering.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Training\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24F39C8-A44B-4AE5-A4B8-7C99FF95E6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E78E9D6-50B8-4FE0-A591-5EC2771B818B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24660" yWindow="6405" windowWidth="18585" windowHeight="9675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="1740" windowWidth="18588" windowHeight="9672" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gathering" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">gathering!$B$1:$L$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">gathering!$B$1:$G$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="109">
   <si>
     <t>id</t>
   </si>
@@ -262,7 +262,116 @@
     <t>OTHER</t>
   </si>
   <si>
-    <t>項目內容</t>
+    <t>活動描述</t>
+  </si>
+  <si>
+    <t>日本北海道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幸福縣快樂市陽光路 220 號</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市流星大道 88 號</t>
+  </si>
+  <si>
+    <t>彩虹縣晴夢市繽紛街 12 巷 6 號</t>
+  </si>
+  <si>
+    <t>幻月縣霜影市月華路 377 號</t>
+  </si>
+  <si>
+    <t>青風縣翡翠市清泉街 5 巷 19 號</t>
+  </si>
+  <si>
+    <t>琉璃縣光海市瑠光路 102 號</t>
+  </si>
+  <si>
+    <t>雲岫縣晴嶺市雲端大道 511 號</t>
+  </si>
+  <si>
+    <t>長樂縣安寧市和風街 33 巷 2 弄 10 號</t>
+  </si>
+  <si>
+    <t>星語縣夢境市星光一路 72 號</t>
+  </si>
+  <si>
+    <t>霧森縣翠柏市林語街 4 巷 28 號</t>
+  </si>
+  <si>
+    <t>晨光縣朝陽市朝日路 260 號</t>
+  </si>
+  <si>
+    <t>活動費用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>參加人數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活動日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-01-12 13:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-15 10:00:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 12:00:00</t>
+  </si>
+  <si>
+    <t>2026-02-11 11:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-12 16:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-09 17:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-09 19:00:00</t>
+  </si>
+  <si>
+    <t>2026-05-08 18:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-29 18:00:00</t>
+  </si>
+  <si>
+    <t>2024-05-16 22:00:00</t>
+  </si>
+  <si>
+    <t>2024-05-23 10:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-24 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活動地點</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>location</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>participantNumbers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>price</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FOOD+D6:I7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -697,26 +806,35 @@
         <v>75</v>
       </c>
       <c r="E1" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="J1" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="L1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="N1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
@@ -732,26 +850,35 @@
         <v>3</v>
       </c>
       <c r="E2" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="I2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="J2" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="K2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="L2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="M2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="N2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
     </row>
     <row r="3" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
@@ -766,28 +893,36 @@
       <c r="D3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2">
+        <v>100</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="J3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H3" s="2" t="b">
+      <c r="L3" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="9"/>
       <c r="O3" s="9"/>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
@@ -803,28 +938,36 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="2">
+        <v>40</v>
+      </c>
+      <c r="G4" s="2">
+        <v>35000</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="J4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="2" t="b">
+      <c r="L4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
     </row>
@@ -841,28 +984,36 @@
       <c r="D5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="2">
+        <v>30</v>
+      </c>
+      <c r="G5" s="2">
+        <v>700</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="J5" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="2" t="b">
+      <c r="L5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
     </row>
@@ -879,28 +1030,36 @@
       <c r="D6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="2">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="I6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="2" t="b">
+      <c r="L6" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="N6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
@@ -917,27 +1076,36 @@
       <c r="D7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="2">
+        <v>50</v>
+      </c>
+      <c r="G7" s="2">
+        <v>5400</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="J7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="2" t="b">
+      <c r="L7" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="N7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
@@ -952,28 +1120,36 @@
       <c r="D8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="2">
+        <v>30</v>
+      </c>
+      <c r="G8" s="2">
+        <v>300</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="J8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="2" t="b">
+      <c r="L8" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="6"/>
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
@@ -990,28 +1166,36 @@
       <c r="D9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="2">
+        <v>30</v>
+      </c>
+      <c r="G9" s="2">
+        <v>200</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="J9" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="2" t="b">
+      <c r="L9" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="N9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="6"/>
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
     </row>
@@ -1028,28 +1212,36 @@
       <c r="D10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="2">
+        <v>30</v>
+      </c>
+      <c r="G10" s="2">
+        <v>200</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="J10" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="2" t="b">
+      <c r="L10" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="M10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="N10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="6"/>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
     </row>
@@ -1066,28 +1258,36 @@
       <c r="D11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="2">
+        <v>70</v>
+      </c>
+      <c r="G11" s="2">
+        <v>200</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="J11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H11" s="2" t="b">
+      <c r="L11" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="M11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="N11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="6"/>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
@@ -1104,28 +1304,36 @@
       <c r="D12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="2">
+        <v>30</v>
+      </c>
+      <c r="G12" s="2">
+        <v>200</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="J12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="2" t="b">
+      <c r="L12" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="M12" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="N12" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="6"/>
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
     </row>
@@ -1142,28 +1350,36 @@
       <c r="D13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="2">
+        <v>60</v>
+      </c>
+      <c r="G13" s="2">
+        <v>200</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="J13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H13" s="2" t="b">
+      <c r="L13" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="M13" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="N13" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
     </row>
@@ -1180,28 +1396,36 @@
       <c r="D14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="2">
+        <v>30</v>
+      </c>
+      <c r="G14" s="2">
+        <v>200</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="J14" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H14" s="2" t="b">
+      <c r="L14" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
     </row>
@@ -1210,7 +1434,7 @@
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="4"/>
+      <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="3"/>
       <c r="H15" s="2"/>
@@ -1228,7 +1452,7 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="4"/>
+      <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
@@ -1245,7 +1469,6 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="4"/>
       <c r="F17" s="2"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
@@ -1262,7 +1485,7 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="4"/>
+      <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
@@ -1279,8 +1502,6 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="2"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
@@ -1296,8 +1517,7 @@
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="2"/>
+      <c r="E20" s="2"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
@@ -1310,8 +1530,6 @@
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="2"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
@@ -1324,8 +1542,7 @@
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="2"/>
+      <c r="E22" s="2"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
@@ -1339,7 +1556,6 @@
       <c r="C23" s="4"/>
       <c r="D23" s="2"/>
       <c r="E23" s="4"/>
-      <c r="F23" s="2"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
@@ -1353,7 +1569,6 @@
       <c r="C24" s="4"/>
       <c r="D24" s="2"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="2"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
@@ -1367,7 +1582,6 @@
       <c r="C25" s="4"/>
       <c r="D25" s="2"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="2"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
@@ -1381,7 +1595,6 @@
       <c r="C26" s="4"/>
       <c r="D26" s="2"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="2"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
@@ -1395,7 +1608,6 @@
       <c r="C27" s="4"/>
       <c r="D27" s="2"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="2"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
@@ -1409,7 +1621,6 @@
       <c r="C28" s="4"/>
       <c r="D28" s="2"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="2"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
@@ -1423,7 +1634,6 @@
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="2"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
@@ -1437,7 +1647,6 @@
       <c r="C30" s="4"/>
       <c r="D30" s="2"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="2"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
@@ -1451,7 +1660,6 @@
       <c r="C31" s="4"/>
       <c r="D31" s="2"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="2"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
@@ -1466,7 +1674,6 @@
       <c r="C32" s="4"/>
       <c r="D32" s="2"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="2"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -1481,7 +1688,6 @@
       <c r="C33" s="4"/>
       <c r="D33" s="2"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="7"/>
@@ -1499,7 +1705,6 @@
       <c r="C34" s="4"/>
       <c r="D34" s="2"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="7"/>
@@ -1517,7 +1722,6 @@
       <c r="C35" s="4"/>
       <c r="D35" s="2"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="7"/>
@@ -1535,7 +1739,6 @@
       <c r="C36" s="4"/>
       <c r="D36" s="2"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="7"/>
@@ -1553,7 +1756,6 @@
       <c r="C37" s="4"/>
       <c r="D37" s="2"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="7"/>
@@ -1589,7 +1791,6 @@
       <c r="C39" s="4"/>
       <c r="D39" s="2"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="7"/>

--- a/data/gathering.xlsx
+++ b/data/gathering.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Training\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E78E9D6-50B8-4FE0-A591-5EC2771B818B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783ABD24-5925-4DDC-B144-724713505F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="1740" windowWidth="18588" windowHeight="9672" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gathering" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="122">
   <si>
     <t>id</t>
   </si>
@@ -164,60 +164,6 @@
     <t>提供最新知識與技能交流，這是一場AI 開發者社群聚會。</t>
   </si>
   <si>
-    <t>2026-01-08 13:00:00</t>
-  </si>
-  <si>
-    <t>2026-12-19 13:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-11 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-01-05 14:30:00</t>
-  </si>
-  <si>
-    <t>2026-01-19 12:00:00</t>
-  </si>
-  <si>
-    <t>2026-01-09 12:00:00</t>
-  </si>
-  <si>
-    <t>2026-02-08 11:00:00</t>
-  </si>
-  <si>
-    <t>2026-01-19 11:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-09 16:00:00</t>
-  </si>
-  <si>
-    <t>2026-02-16 16:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-26 17:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-06 17:00:00</t>
-  </si>
-  <si>
-    <t>2026-04-08 19:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-24 19:00:00</t>
-  </si>
-  <si>
-    <t>2026-05-04 18:00:00</t>
-  </si>
-  <si>
-    <t>2026-04-12 18:00:00</t>
-  </si>
-  <si>
-    <t>2026-04-28 18:00:00</t>
-  </si>
-  <si>
-    <t>2026-04-14 18:00:00</t>
-  </si>
-  <si>
     <t>2024-05-14 22:00:00</t>
   </si>
   <si>
@@ -230,14 +176,6 @@
     <t>2024-05-06 10:00:00</t>
   </si>
   <si>
-    <t>2026-04-14 11:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026-03-01 11:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OPEN</t>
   </si>
   <si>
@@ -318,43 +256,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026-01-12 13:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-15 10:00:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 12:00:00</t>
-  </si>
-  <si>
-    <t>2026-02-11 11:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-12 16:00:00</t>
-  </si>
-  <si>
-    <t>2026-04-09 17:00:00</t>
-  </si>
-  <si>
-    <t>2026-04-09 19:00:00</t>
-  </si>
-  <si>
-    <t>2026-05-08 18:00:00</t>
-  </si>
-  <si>
-    <t>2026-04-29 18:00:00</t>
-  </si>
-  <si>
     <t>2024-05-16 22:00:00</t>
   </si>
   <si>
     <t>2024-05-23 10:00:00</t>
   </si>
   <si>
-    <t>2026-04-24 11:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>活動地點</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -371,7 +278,178 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FOOD+D6:I7</t>
+    <t>達悟族之美</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>參觀達悟族的鐵桶和丁字褲文化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台東縣蘭嶼鄉</t>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-12-03 10:34:28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-06-01 07:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-05-25 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一起去安大林森公園哭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一起分享今年的洗褲哀樂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安大林森公園</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-12-31 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-12-26 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-12-03 10:40:13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-01 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-05 14:30:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-09 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-19 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-02-16 16:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-06 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-24 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-12 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-14 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-24 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-15 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-22 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-02-11 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-12 16:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-09 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-09 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-29 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-05-08 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-14 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-11 00:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-19 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-02-08 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-09 16:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-26 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-08 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-05-04 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-28 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-12-01 13:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-07-11 05:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-16 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FOOD</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -785,11 +863,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P160"/>
+  <dimension ref="A1:P159"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="13" width="28.625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="1" max="14" width="28.625" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -803,16 +881,16 @@
         <v>10</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>15</v>
@@ -821,7 +899,7 @@
         <v>16</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="K1" s="12" t="s">
         <v>18</v>
@@ -850,13 +928,13 @@
         <v>3</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>4</v>
@@ -865,7 +943,7 @@
         <v>17</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="K2" s="13" t="s">
         <v>5</v>
@@ -880,93 +958,94 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="F3" s="2">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="G3" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="L3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="O3" s="9"/>
-    </row>
-    <row r="4" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="F4" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G4" s="2">
-        <v>35000</v>
+        <v>200</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -985,7 +1064,7 @@
         <v>24</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F5" s="2">
         <v>30</v>
@@ -994,25 +1073,25 @@
         <v>700</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="L5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
@@ -1031,7 +1110,7 @@
         <v>26</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="F6" s="2">
         <v>30</v>
@@ -1040,25 +1119,25 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="L6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
@@ -1077,7 +1156,7 @@
         <v>28</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F7" s="2">
         <v>50</v>
@@ -1086,25 +1165,25 @@
         <v>5400</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="L7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
@@ -1121,7 +1200,7 @@
         <v>30</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="F8" s="2">
         <v>30</v>
@@ -1130,30 +1209,30 @@
         <v>300</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="L8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1161,43 +1240,42 @@
         <v>2</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="F9" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G9" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="L9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="O9" s="9"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
@@ -1207,13 +1285,13 @@
         <v>2</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="F10" s="2">
         <v>30</v>
@@ -1222,25 +1300,25 @@
         <v>200</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="L10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
@@ -1253,40 +1331,40 @@
         <v>2</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="F11" s="2">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="G11" s="2">
         <v>200</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="L11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
@@ -1296,43 +1374,43 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="F12" s="2">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2">
         <v>200</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="L12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
@@ -1345,122 +1423,179 @@
         <v>10</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="F13" s="2">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G13" s="2">
         <v>200</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="L13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="F14" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G14" s="2">
-        <v>200</v>
+        <v>35000</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="L14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="6"/>
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>40</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="2">
+        <v>300</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="O15" s="6"/>
       <c r="P15" s="6"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="6"/>
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>40</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
     </row>
@@ -1469,6 +1604,7 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
@@ -1485,8 +1621,6 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
@@ -1502,9 +1636,7 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="2"/>
-      <c r="G19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
+      <c r="E19" s="2"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -1517,7 +1649,6 @@
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
@@ -1530,6 +1661,7 @@
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
@@ -1542,7 +1674,7 @@
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
+      <c r="E22" s="4"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
@@ -1647,6 +1779,7 @@
       <c r="C30" s="4"/>
       <c r="D30" s="2"/>
       <c r="E30" s="4"/>
+      <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
@@ -1674,6 +1807,9 @@
       <c r="C32" s="4"/>
       <c r="D32" s="2"/>
       <c r="E32" s="4"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="7"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -1756,6 +1892,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="2"/>
       <c r="E37" s="4"/>
+      <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="7"/>
@@ -1773,7 +1910,6 @@
       <c r="C38" s="4"/>
       <c r="D38" s="2"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="7"/>
@@ -1791,6 +1927,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="2"/>
       <c r="E39" s="4"/>
+      <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="7"/>
@@ -2860,9 +2997,6 @@
       <c r="K98" s="3"/>
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
-      <c r="N98" s="6"/>
-      <c r="O98" s="6"/>
-      <c r="P98" s="6"/>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="2"/>
@@ -3405,19 +3539,13 @@
       <c r="M134" s="3"/>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A135" s="2"/>
-      <c r="B135" s="4"/>
-      <c r="C135" s="4"/>
-      <c r="D135" s="2"/>
-      <c r="E135" s="4"/>
-      <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
-      <c r="H135" s="2"/>
-      <c r="I135" s="7"/>
-      <c r="J135" s="3"/>
-      <c r="K135" s="3"/>
-      <c r="L135" s="3"/>
-      <c r="M135" s="3"/>
+      <c r="F135" s="8"/>
+      <c r="G135" s="8"/>
+      <c r="H135" s="8"/>
+      <c r="I135" s="8"/>
+      <c r="J135" s="10"/>
+      <c r="K135" s="8"/>
+      <c r="L135" s="8"/>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F136" s="8"/>
@@ -3500,89 +3628,80 @@
       <c r="K144" s="8"/>
       <c r="L144" s="8"/>
     </row>
-    <row r="145" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="F145" s="8"/>
-      <c r="G145" s="8"/>
-      <c r="H145" s="8"/>
-      <c r="I145" s="8"/>
-      <c r="J145" s="10"/>
-      <c r="K145" s="8"/>
-      <c r="L145" s="8"/>
-    </row>
-    <row r="146" spans="6:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J145" s="5"/>
+      <c r="K145" s="5"/>
+      <c r="L145" s="5"/>
+    </row>
+    <row r="146" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J146" s="5"/>
       <c r="K146" s="5"/>
       <c r="L146" s="5"/>
     </row>
-    <row r="147" spans="6:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J147" s="5"/>
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
     </row>
-    <row r="148" spans="6:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J148" s="5"/>
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
     </row>
-    <row r="149" spans="6:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J149" s="5"/>
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
     </row>
-    <row r="150" spans="6:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J150" s="5"/>
       <c r="K150" s="5"/>
       <c r="L150" s="5"/>
     </row>
-    <row r="151" spans="6:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J151" s="5"/>
       <c r="K151" s="5"/>
       <c r="L151" s="5"/>
     </row>
-    <row r="152" spans="6:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J152" s="5"/>
       <c r="K152" s="5"/>
       <c r="L152" s="5"/>
     </row>
-    <row r="153" spans="6:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J153" s="5"/>
       <c r="K153" s="5"/>
       <c r="L153" s="5"/>
     </row>
-    <row r="154" spans="6:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J154" s="5"/>
       <c r="K154" s="5"/>
       <c r="L154" s="5"/>
     </row>
-    <row r="155" spans="6:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J155" s="5"/>
       <c r="K155" s="5"/>
       <c r="L155" s="5"/>
     </row>
-    <row r="156" spans="6:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J156" s="5"/>
       <c r="K156" s="5"/>
       <c r="L156" s="5"/>
     </row>
-    <row r="157" spans="6:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J157" s="5"/>
       <c r="K157" s="5"/>
       <c r="L157" s="5"/>
     </row>
-    <row r="158" spans="6:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J158" s="5"/>
       <c r="K158" s="5"/>
       <c r="L158" s="5"/>
     </row>
-    <row r="159" spans="6:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
       <c r="L159" s="5"/>
-    </row>
-    <row r="160" spans="6:12" x14ac:dyDescent="0.3">
-      <c r="J160" s="5"/>
-      <c r="K160" s="5"/>
-      <c r="L160" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
